--- a/resources/templates/standard/L1100-01.xlsx
+++ b/resources/templates/standard/L1100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="99">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">장 비 제 작 사 양 서
 (SPECIFICATION FOR QUOTATION)</t>
@@ -1227,7 +1230,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1235,7 +1240,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -1390,7 +1395,7 @@
     </row>
     <row r="5" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1413,7 +1418,7 @@
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
@@ -1474,7 +1479,7 @@
     </row>
     <row r="7" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1497,7 +1502,7 @@
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
       <c r="V7" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
@@ -1558,7 +1563,7 @@
     </row>
     <row r="9" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1640,7 +1645,7 @@
     </row>
     <row r="11" ht="10" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -1690,12 +1695,12 @@
       <c r="G12" s="8"/>
       <c r="H12" s="10"/>
       <c r="I12" s="11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
@@ -1713,12 +1718,12 @@
       <c r="Z12" s="12"/>
       <c r="AA12" s="12"/>
       <c r="AB12" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC12" s="12"/>
       <c r="AD12" s="12"/>
       <c r="AE12" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF12" s="12"/>
       <c r="AG12" s="12"/>
@@ -1738,7 +1743,7 @@
       <c r="G13" s="8"/>
       <c r="H13" s="10"/>
       <c r="I13" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -1820,7 +1825,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="10"/>
       <c r="I15" s="18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
@@ -1942,7 +1947,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="10"/>
       <c r="I18" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="18"/>
       <c r="K18" s="18"/>
@@ -2104,7 +2109,7 @@
       <c r="G22" s="8"/>
       <c r="H22" s="10"/>
       <c r="I22" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
@@ -2266,7 +2271,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="10"/>
       <c r="I26" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -2340,7 +2345,7 @@
     </row>
     <row r="28" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2542,7 +2547,7 @@
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -2551,7 +2556,7 @@
       <c r="F33" s="25"/>
       <c r="G33" s="25"/>
       <c r="H33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -2633,14 +2638,14 @@
       <c r="F35" s="25"/>
       <c r="G35" s="25"/>
       <c r="H35" s="27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I35" s="27"/>
       <c r="J35" s="27"/>
       <c r="K35" s="27"/>
       <c r="L35" s="27"/>
       <c r="M35" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -2722,7 +2727,7 @@
       <c r="K37" s="27"/>
       <c r="L37" s="27"/>
       <c r="M37" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
@@ -2792,7 +2797,7 @@
     </row>
     <row r="39" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -2801,7 +2806,7 @@
       <c r="F39" s="25"/>
       <c r="G39" s="25"/>
       <c r="H39" s="27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I39" s="27"/>
       <c r="J39" s="27"/>
@@ -2837,17 +2842,17 @@
     <row r="40" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="28"/>
       <c r="B40" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C40" s="29"/>
       <c r="D40" s="30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="30"/>
       <c r="F40" s="30"/>
       <c r="G40" s="30"/>
       <c r="H40" s="31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I40" s="31"/>
       <c r="J40" s="31"/>
@@ -2864,7 +2869,7 @@
       <c r="U40" s="32"/>
       <c r="V40" s="32"/>
       <c r="W40" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X40" s="31"/>
       <c r="Y40" s="31"/>
@@ -2927,13 +2932,13 @@
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
       <c r="D42" s="30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E42" s="30"/>
       <c r="F42" s="30"/>
       <c r="G42" s="30"/>
       <c r="H42" s="31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I42" s="31"/>
       <c r="J42" s="31"/>
@@ -2950,7 +2955,7 @@
       <c r="U42" s="32"/>
       <c r="V42" s="32"/>
       <c r="W42" s="31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X42" s="31"/>
       <c r="Y42" s="31"/>
@@ -3013,13 +3018,13 @@
       <c r="B44" s="29"/>
       <c r="C44" s="29"/>
       <c r="D44" s="30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="30"/>
       <c r="G44" s="30"/>
       <c r="H44" s="31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I44" s="31"/>
       <c r="J44" s="31"/>
@@ -3036,7 +3041,7 @@
       <c r="U44" s="32"/>
       <c r="V44" s="32"/>
       <c r="W44" s="31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X44" s="31"/>
       <c r="Y44" s="31"/>
@@ -3137,7 +3142,7 @@
     <row r="47" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="41"/>
       <c r="B47" s="42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C47" s="42"/>
       <c r="D47" s="42"/>
@@ -3145,7 +3150,7 @@
       <c r="F47" s="42"/>
       <c r="G47" s="42"/>
       <c r="H47" s="42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I47" s="42"/>
       <c r="J47" s="42"/>
@@ -3181,23 +3186,23 @@
     <row r="48" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="43"/>
       <c r="B48" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C48" s="27"/>
       <c r="D48" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E48" s="27"/>
       <c r="F48" s="27"/>
       <c r="G48" s="27"/>
       <c r="H48" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I48" s="30"/>
       <c r="J48" s="30"/>
       <c r="K48" s="30"/>
       <c r="L48" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M48" s="44"/>
       <c r="N48" s="44"/>
@@ -3279,7 +3284,7 @@
       <c r="J50" s="30"/>
       <c r="K50" s="30"/>
       <c r="L50" s="44" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M50" s="44"/>
       <c r="N50" s="44"/>
@@ -3351,23 +3356,23 @@
     <row r="52" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" s="43"/>
       <c r="B52" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C52" s="27"/>
       <c r="D52" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E52" s="27"/>
       <c r="F52" s="27"/>
       <c r="G52" s="27"/>
       <c r="H52" s="30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I52" s="30"/>
       <c r="J52" s="30"/>
       <c r="K52" s="30"/>
       <c r="L52" s="44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M52" s="44"/>
       <c r="N52" s="44"/>
@@ -3569,7 +3574,7 @@
       <c r="J57" s="30"/>
       <c r="K57" s="30"/>
       <c r="L57" s="44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M57" s="44"/>
       <c r="N57" s="44"/>
@@ -3683,19 +3688,19 @@
       <c r="B60" s="27"/>
       <c r="C60" s="27"/>
       <c r="D60" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E60" s="27"/>
       <c r="F60" s="27"/>
       <c r="G60" s="27"/>
       <c r="H60" s="30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I60" s="30"/>
       <c r="J60" s="30"/>
       <c r="K60" s="30"/>
       <c r="L60" s="44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M60" s="44"/>
       <c r="N60" s="44"/>
@@ -3767,23 +3772,23 @@
     <row r="62" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" s="43"/>
       <c r="B62" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C62" s="27"/>
       <c r="D62" s="47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E62" s="47"/>
       <c r="F62" s="47"/>
       <c r="G62" s="47"/>
       <c r="H62" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I62" s="30"/>
       <c r="J62" s="30"/>
       <c r="K62" s="30"/>
       <c r="L62" s="44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M62" s="44"/>
       <c r="N62" s="44"/>
@@ -4021,13 +4026,13 @@
       <c r="F68" s="47"/>
       <c r="G68" s="47"/>
       <c r="H68" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I68" s="30"/>
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
       <c r="L68" s="44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M68" s="44"/>
       <c r="N68" s="44"/>
@@ -4979,7 +4984,7 @@
     <row r="92" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" s="41"/>
       <c r="B92" s="42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C92" s="42"/>
       <c r="D92" s="42"/>
@@ -4987,7 +4992,7 @@
       <c r="F92" s="42"/>
       <c r="G92" s="42"/>
       <c r="H92" s="42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I92" s="42"/>
       <c r="J92" s="42"/>
@@ -5023,23 +5028,23 @@
     <row r="93" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" s="51"/>
       <c r="B93" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C93" s="27"/>
       <c r="D93" s="47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E93" s="47"/>
       <c r="F93" s="47"/>
       <c r="G93" s="47"/>
       <c r="H93" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I93" s="30"/>
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
       <c r="L93" s="44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M93" s="44"/>
       <c r="N93" s="44"/>
@@ -6041,7 +6046,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
       <c r="L118" s="44" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M118" s="44"/>
       <c r="N118" s="44"/>
@@ -6123,7 +6128,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
       <c r="L120" s="44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M120" s="44"/>
       <c r="N120" s="44"/>
@@ -6241,13 +6246,13 @@
       <c r="F123" s="47"/>
       <c r="G123" s="47"/>
       <c r="H123" s="44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I123" s="44"/>
       <c r="J123" s="44"/>
       <c r="K123" s="44"/>
       <c r="L123" s="44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M123" s="44"/>
       <c r="N123" s="44"/>
@@ -6519,23 +6524,23 @@
     <row r="130" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A130" s="51"/>
       <c r="B130" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C130" s="27"/>
       <c r="D130" s="47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E130" s="47"/>
       <c r="F130" s="47"/>
       <c r="G130" s="47"/>
       <c r="H130" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I130" s="30"/>
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
       <c r="L130" s="44" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M130" s="44"/>
       <c r="N130" s="44"/>
@@ -6807,7 +6812,7 @@
     <row r="137" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A137" s="41"/>
       <c r="B137" s="42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C137" s="42"/>
       <c r="D137" s="42"/>
@@ -6815,7 +6820,7 @@
       <c r="F137" s="42"/>
       <c r="G137" s="42"/>
       <c r="H137" s="53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I137" s="53"/>
       <c r="J137" s="53"/>
@@ -6851,7 +6856,7 @@
     <row r="138" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A138" s="28"/>
       <c r="B138" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C138" s="27"/>
       <c r="D138" s="27"/>
@@ -7093,7 +7098,7 @@
     <row r="144" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A144" s="51"/>
       <c r="B144" s="47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C144" s="47"/>
       <c r="D144" s="47"/>
@@ -7335,7 +7340,7 @@
     <row r="150" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A150" s="51"/>
       <c r="B150" s="47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C150" s="47"/>
       <c r="D150" s="47"/>
@@ -7457,7 +7462,7 @@
     <row r="153" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A153" s="51"/>
       <c r="B153" s="47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C153" s="47"/>
       <c r="D153" s="47"/>
@@ -7539,7 +7544,7 @@
     <row r="155" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A155" s="51"/>
       <c r="B155" s="47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C155" s="47"/>
       <c r="D155" s="47"/>
@@ -7660,7 +7665,7 @@
     </row>
     <row r="158" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A158" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B158" s="25"/>
       <c r="C158" s="25"/>
@@ -8223,7 +8228,7 @@
     <row r="172" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A172" s="43"/>
       <c r="B172" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C172" s="27"/>
       <c r="D172" s="27"/>
@@ -8231,7 +8236,7 @@
       <c r="F172" s="27"/>
       <c r="G172" s="27"/>
       <c r="H172" s="56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I172" s="56"/>
       <c r="J172" s="56"/>
@@ -8267,23 +8272,23 @@
     <row r="173" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A173" s="28"/>
       <c r="B173" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C173" s="27"/>
       <c r="D173" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E173" s="27"/>
       <c r="F173" s="27"/>
       <c r="G173" s="27"/>
       <c r="H173" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I173" s="30"/>
       <c r="J173" s="30"/>
       <c r="K173" s="30"/>
       <c r="L173" s="57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M173" s="57"/>
       <c r="N173" s="57"/>
@@ -8325,7 +8330,7 @@
       <c r="J174" s="30"/>
       <c r="K174" s="30"/>
       <c r="L174" s="59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M174" s="59"/>
       <c r="N174" s="59"/>
@@ -8367,7 +8372,7 @@
       <c r="J175" s="30"/>
       <c r="K175" s="30"/>
       <c r="L175" s="59" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M175" s="59"/>
       <c r="N175" s="59"/>
@@ -8409,7 +8414,7 @@
       <c r="J176" s="30"/>
       <c r="K176" s="30"/>
       <c r="L176" s="59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M176" s="59"/>
       <c r="N176" s="59"/>
@@ -8451,7 +8456,7 @@
       <c r="J177" s="30"/>
       <c r="K177" s="30"/>
       <c r="L177" s="59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M177" s="59"/>
       <c r="N177" s="59"/>
@@ -8493,7 +8498,7 @@
       <c r="J178" s="30"/>
       <c r="K178" s="30"/>
       <c r="L178" s="59" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M178" s="59"/>
       <c r="N178" s="59"/>
@@ -8535,7 +8540,7 @@
       <c r="J179" s="30"/>
       <c r="K179" s="30"/>
       <c r="L179" s="59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M179" s="59"/>
       <c r="N179" s="59"/>
@@ -8577,7 +8582,7 @@
       <c r="J180" s="30"/>
       <c r="K180" s="30"/>
       <c r="L180" s="59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M180" s="59"/>
       <c r="N180" s="59"/>
@@ -8619,7 +8624,7 @@
       <c r="J181" s="30"/>
       <c r="K181" s="30"/>
       <c r="L181" s="60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M181" s="60"/>
       <c r="N181" s="60"/>
@@ -8651,7 +8656,7 @@
     <row r="182" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A182" s="41"/>
       <c r="B182" s="42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C182" s="42"/>
       <c r="D182" s="42"/>
@@ -8659,7 +8664,7 @@
       <c r="F182" s="42"/>
       <c r="G182" s="42"/>
       <c r="H182" s="42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I182" s="42"/>
       <c r="J182" s="42"/>
@@ -8695,23 +8700,23 @@
     <row r="183" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A183" s="28"/>
       <c r="B183" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C183" s="27"/>
       <c r="D183" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E183" s="27"/>
       <c r="F183" s="27"/>
       <c r="G183" s="27"/>
       <c r="H183" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I183" s="30"/>
       <c r="J183" s="30"/>
       <c r="K183" s="30"/>
       <c r="L183" s="57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M183" s="57"/>
       <c r="N183" s="57"/>
@@ -8753,7 +8758,7 @@
       <c r="J184" s="30"/>
       <c r="K184" s="30"/>
       <c r="L184" s="59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M184" s="59"/>
       <c r="N184" s="59"/>
@@ -8795,7 +8800,7 @@
       <c r="J185" s="30"/>
       <c r="K185" s="30"/>
       <c r="L185" s="59" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M185" s="59"/>
       <c r="N185" s="59"/>
@@ -8837,7 +8842,7 @@
       <c r="J186" s="30"/>
       <c r="K186" s="30"/>
       <c r="L186" s="59" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M186" s="59"/>
       <c r="N186" s="59"/>
@@ -8879,7 +8884,7 @@
       <c r="J187" s="30"/>
       <c r="K187" s="30"/>
       <c r="L187" s="59" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M187" s="59"/>
       <c r="N187" s="59"/>
@@ -8921,7 +8926,7 @@
       <c r="J188" s="30"/>
       <c r="K188" s="30"/>
       <c r="L188" s="62" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M188" s="62"/>
       <c r="N188" s="62"/>
@@ -9073,7 +9078,7 @@
     <row r="192" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A192" s="28"/>
       <c r="B192" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C192" s="27"/>
       <c r="D192" s="27"/>
@@ -9081,13 +9086,13 @@
       <c r="F192" s="27"/>
       <c r="G192" s="27"/>
       <c r="H192" s="30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I192" s="30"/>
       <c r="J192" s="30"/>
       <c r="K192" s="30"/>
       <c r="L192" s="57" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M192" s="57"/>
       <c r="N192" s="57"/>
@@ -9129,7 +9134,7 @@
       <c r="J193" s="30"/>
       <c r="K193" s="30"/>
       <c r="L193" s="59" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M193" s="59"/>
       <c r="N193" s="59"/>
@@ -9171,7 +9176,7 @@
       <c r="J194" s="30"/>
       <c r="K194" s="30"/>
       <c r="L194" s="59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M194" s="59"/>
       <c r="N194" s="59"/>
@@ -9213,7 +9218,7 @@
       <c r="J195" s="30"/>
       <c r="K195" s="30"/>
       <c r="L195" s="59" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M195" s="59"/>
       <c r="N195" s="59"/>
@@ -9255,7 +9260,7 @@
       <c r="J196" s="30"/>
       <c r="K196" s="30"/>
       <c r="L196" s="59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M196" s="59"/>
       <c r="N196" s="59"/>
@@ -9297,7 +9302,7 @@
       <c r="J197" s="30"/>
       <c r="K197" s="30"/>
       <c r="L197" s="59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M197" s="59"/>
       <c r="N197" s="59"/>
@@ -9339,7 +9344,7 @@
       <c r="J198" s="30"/>
       <c r="K198" s="30"/>
       <c r="L198" s="62" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M198" s="62"/>
       <c r="N198" s="62"/>
@@ -9421,7 +9426,7 @@
       <c r="J200" s="30"/>
       <c r="K200" s="30"/>
       <c r="L200" s="59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M200" s="59"/>
       <c r="N200" s="59"/>
@@ -9463,7 +9468,7 @@
       <c r="J201" s="30"/>
       <c r="K201" s="30"/>
       <c r="L201" s="59" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M201" s="59"/>
       <c r="N201" s="59"/>
@@ -9505,7 +9510,7 @@
       <c r="J202" s="30"/>
       <c r="K202" s="30"/>
       <c r="L202" s="62" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M202" s="62"/>
       <c r="N202" s="62"/>
@@ -9617,7 +9622,7 @@
     <row r="205" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A205" s="28"/>
       <c r="B205" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C205" s="27"/>
       <c r="D205" s="27"/>
@@ -9625,13 +9630,13 @@
       <c r="F205" s="27"/>
       <c r="G205" s="27"/>
       <c r="H205" s="44" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I205" s="44"/>
       <c r="J205" s="44"/>
       <c r="K205" s="44"/>
       <c r="L205" s="57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M205" s="57"/>
       <c r="N205" s="57"/>
@@ -9673,7 +9678,7 @@
       <c r="J206" s="44"/>
       <c r="K206" s="44"/>
       <c r="L206" s="60" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M206" s="60"/>
       <c r="N206" s="60"/>
@@ -9744,7 +9749,7 @@
     </row>
     <row r="208" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A208" s="25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B208" s="25"/>
       <c r="C208" s="25"/>
@@ -10426,7 +10431,7 @@
     </row>
     <row r="225" ht="16" customHeight="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
